--- a/tiflow/develop/2.0.0-ballot.1/CodeSystem-ti-fhir-configuration-cs.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/CodeSystem-ti-fhir-configuration-cs.xlsx
@@ -23,7 +23,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/CodeSystem/ti-fhir-configuration-cs</t>
+    <t>https://gematik.de/fhir/tiflow/CodeSystem/ti-fhir-configuration-cs</t>
   </si>
   <si>
     <t>Version</t>
